--- a/Assets/Project/Csv/Item/2. Consumable.xlsx
+++ b/Assets/Project/Csv/Item/2. Consumable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021E1723-773F-46FE-886F-BB7AB68FC77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708E5449-7B30-4793-8672-F5B605D6FDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
+    <workbookView xWindow="1800" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -209,10 +209,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -585,7 +585,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>7</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>301</v>
+        <v>1201</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
-        <v>401</v>
+        <v>1301</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>11</v>

--- a/Assets/Project/Csv/Item/2. Consumable.xlsx
+++ b/Assets/Project/Csv/Item/2. Consumable.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\Item\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708E5449-7B30-4793-8672-F5B605D6FDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
+    <workbookView xWindow="1800" yWindow="3120" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>maxStack</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,14 +86,22 @@
   </si>
   <si>
     <t>effectValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지렁이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바다에 던져</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,7 +277,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -327,7 +329,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -541,16 +543,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483D797F-3D37-4ED4-9810-065C3F986DE7}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
@@ -560,7 +562,7 @@
     <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -583,7 +585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -601,7 +603,7 @@
       </c>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="4">
         <v>1101</v>
       </c>
@@ -619,7 +621,7 @@
       </c>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>1201</v>
       </c>
@@ -637,7 +639,7 @@
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="4">
         <v>1301</v>
       </c>
@@ -654,6 +656,23 @@
         <v>0</v>
       </c>
       <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>1401</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>99</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
